--- a/main/CodeSystem-bc-client-registry-patient-change-notification-events.xlsx
+++ b/main/CodeSystem-bc-client-registry-patient-change-notification-events.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -177,7 +177,7 @@
     <t>A Newborn distribution is a non-source distribution that informs subscribers that a newborn record has been created and has been assigned a PHN. Typically, subscribers would limit their source subscription to MOH_CRS for this distribution.</t>
   </si>
   <si>
-    <t>NEWBORN_GENDER</t>
+    <t>NEWBORNGENDER</t>
   </si>
   <si>
     <t>Newborn Gender</t>
